--- a/experiments/results/resnet_imagenet34/ImageNet-1K/ReAct+DICE/adaptive/max/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/ReAct+DICE/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -651,6 +651,80 @@
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>dice_p=5,ash_p=None,react_th=2.2,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=2.2,scale_th=0.1,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>96.31</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=2.0,scale_th=1.2,type=max</t>
         </is>
       </c>
     </row>
